--- a/data/trans_orig/IP26B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP26B-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16429</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24802</t>
+          <t>25196</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38962</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28814</t>
+          <t>28023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43869</t>
+          <t>44025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63872</t>
+          <t>63350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35271</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49634</t>
+          <t>50269</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40260</t>
+          <t>40322</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55045</t>
+          <t>55071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80480</t>
+          <t>79958</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101148</t>
+          <t>100362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11771</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>22122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16579</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32478</t>
+          <t>33228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26932</t>
+          <t>27013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46384</t>
+          <t>45941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49730</t>
+          <t>48646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73504</t>
+          <t>72429</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>127553</t>
+          <t>128901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160445</t>
+          <t>160303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137736</t>
+          <t>136842</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>170337</t>
+          <t>169915</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>274781</t>
+          <t>274223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319839</t>
+          <t>317880</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>198773</t>
+          <t>197747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>230957</t>
+          <t>230752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>226820</t>
+          <t>227064</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>259364</t>
+          <t>261585</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>437161</t>
+          <t>435040</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>482951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,19%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34599</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25779</t>
+          <t>25292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42765</t>
+          <t>42294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48058</t>
+          <t>47951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70388</t>
+          <t>72656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34346</t>
+          <t>33004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48462</t>
+          <t>48407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41458</t>
+          <t>42028</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60054</t>
+          <t>60525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42524</t>
+          <t>42548</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61946</t>
+          <t>61611</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90433</t>
+          <t>90271</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117395</t>
+          <t>117309</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75638</t>
+          <t>75534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96105</t>
+          <t>96718</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69255</t>
+          <t>69387</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89337</t>
+          <t>89717</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>151029</t>
+          <t>151204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>181205</t>
+          <t>180202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65360</t>
+          <t>65846</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43332</t>
+          <t>44261</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66691</t>
+          <t>66800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92568</t>
+          <t>92002</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125814</t>
+          <t>123477</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>206365</t>
+          <t>206134</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244918</t>
+          <t>245191</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>206573</t>
+          <t>204982</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>246389</t>
+          <t>244467</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>423682</t>
+          <t>419930</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>479654</t>
+          <t>476756</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>323542</t>
+          <t>322592</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>364153</t>
+          <t>363332</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>350751</t>
+          <t>351875</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>393566</t>
+          <t>393252</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>684842</t>
+          <t>684531</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>745690</t>
+          <t>745330</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>54832</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>37793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59550</t>
+          <t>59320</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78520</t>
+          <t>77864</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107358</t>
+          <t>106978</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21528</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28829</t>
+          <t>27323</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12829</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>16450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>31912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45776</t>
+          <t>45781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61005</t>
+          <t>61302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50751</t>
+          <t>50397</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65604</t>
+          <t>64905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100825</t>
+          <t>100705</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121747</t>
+          <t>121894</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>24113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>24776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42031</t>
+          <t>42403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,82 +4158,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3510</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>8007</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1241</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4480</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3510</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1282</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>7823</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24837</t>
+          <t>25414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>42785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>25183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42755</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53826</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78373</t>
+          <t>79095</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56759</t>
+          <t>57031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82800</t>
+          <t>80557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63707</t>
+          <t>63833</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90271</t>
+          <t>90482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126534</t>
+          <t>127389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162712</t>
+          <t>163000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>261648</t>
+          <t>261327</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>295842</t>
+          <t>293834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>277541</t>
+          <t>277702</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>313375</t>
+          <t>314692</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>552774</t>
+          <t>551365</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>601127</t>
+          <t>599897</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49330</t>
+          <t>47881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72508</t>
+          <t>72605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52312</t>
+          <t>53315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77638</t>
+          <t>78399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107775</t>
+          <t>108794</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141485</t>
+          <t>142104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>27577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>36843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23010</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34219</t>
+          <t>33190</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35239</t>
+          <t>34400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40799</t>
+          <t>41287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63381</t>
+          <t>63126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95909</t>
+          <t>96403</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116976</t>
+          <t>116964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97113</t>
+          <t>98593</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>118581</t>
+          <t>119886</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>200788</t>
+          <t>201416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>229808</t>
+          <t>231479</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>10047</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>28087</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47008</t>
+          <t>46474</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>36904</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57669</t>
+          <t>58211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>39428</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61493</t>
+          <t>61617</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82347</t>
+          <t>81308</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112534</t>
+          <t>112189</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93959</t>
+          <t>93072</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124048</t>
+          <t>123575</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>97187</t>
+          <t>94182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>126878</t>
+          <t>128590</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>198242</t>
+          <t>198523</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>242690</t>
+          <t>243681</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>419102</t>
+          <t>416961</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>460534</t>
+          <t>458153</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,47 +5978,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>64,71%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>464208</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>442498</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>486405</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>62,1%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>59,19%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>65,04%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>464208</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>443204</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>486523</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>62,1%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>59,29%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>873433</t>
+          <t>873237</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>932943</t>
+          <t>932168</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84730</t>
+          <t>84758</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>115960</t>
+          <t>114826</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79551</t>
+          <t>80503</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110218</t>
+          <t>111010</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>172746</t>
+          <t>174195</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>214664</t>
+          <t>214190</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22860</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36348</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32837</t>
+          <t>32386</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>53776</t>
+          <t>53255</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25159</t>
+          <t>24523</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39114</t>
+          <t>38244</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>24206</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36036</t>
+          <t>36486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>33135</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46211</t>
+          <t>46408</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61162</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79702</t>
+          <t>79427</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29305</t>
+          <t>29204</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>47893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26753</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>44928</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59244</t>
+          <t>58459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85789</t>
+          <t>87018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106115</t>
+          <t>105945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136914</t>
+          <t>136229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109494</t>
+          <t>109883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141896</t>
+          <t>140807</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>225340</t>
+          <t>224425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269021</t>
+          <t>268223</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210137</t>
+          <t>212369</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>245570</t>
+          <t>244912</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>210489</t>
+          <t>208541</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>245760</t>
+          <t>247745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>432925</t>
+          <t>432485</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>483097</t>
+          <t>483027</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>56904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82748</t>
+          <t>81946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71665</t>
+          <t>70564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99642</t>
+          <t>99796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136803</t>
+          <t>135828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173312</t>
+          <t>173946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21199</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>22259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31865</t>
+          <t>33021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>43598</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>29086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>48030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60982</t>
+          <t>60346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86224</t>
+          <t>85152</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72453</t>
+          <t>71298</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93601</t>
+          <t>93139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82653</t>
+          <t>83164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105922</t>
+          <t>104842</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>162940</t>
+          <t>161597</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>193639</t>
+          <t>193020</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31199</t>
+          <t>31409</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48918</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49003</t>
+          <t>49296</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66346</t>
+          <t>67160</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90955</t>
+          <t>92422</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41239</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62186</t>
+          <t>62021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41120</t>
+          <t>41197</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65391</t>
+          <t>64772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88528</t>
+          <t>87736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118930</t>
+          <t>118757</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156700</t>
+          <t>154884</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>193112</t>
+          <t>193212</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>155658</t>
+          <t>155689</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>193661</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>322963</t>
+          <t>321802</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>375382</t>
+          <t>375272</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>319840</t>
+          <t>320830</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>363187</t>
+          <t>363861</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>339596</t>
+          <t>337743</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>384117</t>
+          <t>385978</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>672752</t>
+          <t>674256</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>733485</t>
+          <t>735607</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99880</t>
+          <t>99945</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131860</t>
+          <t>132736</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120872</t>
+          <t>120209</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155140</t>
+          <t>153957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>228038</t>
+          <t>228897</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>276008</t>
+          <t>276986</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>26841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45504</t>
+          <t>47258</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
